--- a/experiments/results/resnet_imagenet34/ImageNet-1K/baseline/energy/adaptive/max/results.xlsx
+++ b/experiments/results/resnet_imagenet34/ImageNet-1K/baseline/energy/adaptive/max/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -651,6 +651,117 @@
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=4.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>90.38</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>51.21</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>95.95999999999999</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>91.93000000000001</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>90.88</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>87.81</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>95.61</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=5.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>90.79000000000001</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>94.92</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>92.27</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=6.0,type=max</t>
         </is>
       </c>
     </row>
